--- a/reports/pdf_rolling5_20260720.xlsx
+++ b/reports/pdf_rolling5_20260720.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,7 +171,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,21 +560,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>코스닥 액티브 ETF 최근 5거래일 PDF 변화   ·   2026-07-13 ~ 2026-07-20  (최근 5거래일)</t>
+          <t>코스닥 액티브 ETF 최근 5거래일 PDF 변화   ·   2026-07-10 ~ 2026-07-20  (최근 5거래일)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-13 ~ 2026-07-20  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-10 ~ 2026-07-20  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 151억(3.3%)      오늘 2026-07-20  vs  5일전 2026-07-13      매수 13종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 151억(3.3%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 16종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -690,7 +695,7 @@
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.96%→1.04%</t>
+          <t>1.91%→1.04%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
@@ -706,19 +711,19 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>7989686400</v>
+        <v>8705743200</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>3.11%→3.46%</t>
+          <t>2.84%→3.46%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>199→411</t>
+          <t>180→411</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -734,7 +739,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.32%</t>
+          <t>0.54%→0.32%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -750,19 +755,19 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1389486720</v>
+        <v>1892261520</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.32%</t>
+          <t>0.80%→1.32%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>493→645</t>
+          <t>438→645</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -778,7 +783,7 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>1.33%→0.95%</t>
+          <t>1.36%→0.95%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -790,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4433510400</v>
+        <v>952512000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>1.05%→2.01%</t>
+          <t>0.41%→0.67%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>66→130</t>
+          <t>173→253</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -818,7 +823,7 @@
         <v>-54</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-911282400</v>
+        <v>-794914560</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -834,23 +839,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>985790880</v>
+        <v>4849152000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.69%→0.90%</t>
+          <t>0.99%→2.01%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>182→241</t>
+          <t>60→130</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -878,44 +883,44 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>440536800</v>
+        <v>985790880</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.67%</t>
+          <t>0.73%→0.90%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>216→253</t>
+          <t>182→241</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>알멕  (편출)</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-701100000</v>
+        <v>-810816000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.27%</t>
+          <t>0.19%→0.00%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>81→51</t>
+          <t>32→0</t>
         </is>
       </c>
     </row>
@@ -933,7 +938,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.37%→1.99%</t>
+          <t>1.29%→1.99%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -943,371 +948,419 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-5353353600</v>
+        <v>-701100000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>9.28%→9.52%</t>
+          <t>0.52%→0.27%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>251→223</t>
+          <t>81→51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>718566000</v>
+        <v>3668745600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.36%→0.56%</t>
+          <t>3.34%→4.79%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>57→80</t>
+          <t>126→152</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-20</v>
+        <v>-28</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1212288000</v>
+        <v>-5353353600</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.50%</t>
+          <t>8.37%→9.52%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>57→37</t>
+          <t>251→223</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2681006400</v>
+        <v>891504000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.77%→4.79%</t>
+          <t>0.48%→0.68%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>133→152</t>
+          <t>58→82</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-15</v>
+        <v>-22</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-426564000</v>
+        <v>-1651742400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.48%</t>
+          <t>1.24%→0.84%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>90→75</t>
+          <t>72→50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>가온칩스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>881172000</v>
+        <v>718566000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.87%→1.91%</t>
+          <t>0.38%→0.56%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>157→175</t>
+          <t>57→80</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알멕  (편출)</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-459774000</v>
+        <v>-1212288000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.90%→0.50%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>15→0</t>
+          <t>57→37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>445752000</v>
+        <v>407700720</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.58%→0.68%</t>
+          <t>1.10%→1.09%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>70→82</t>
+          <t>231→252</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-13</v>
+        <v>-15</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-410623200</v>
+        <v>-426564000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.46%</t>
+          <t>0.65%→0.48%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>78→65</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>가온칩스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>435666000</v>
+        <v>881172000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.61%→0.72%</t>
+          <t>2.01%→1.91%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>157→175</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-825871200</v>
+        <v>-410623200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.84%</t>
+          <t>0.61%→0.46%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>61→50</t>
+          <t>78→65</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>435666000</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>0.62%→0.72%</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>70→81</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>보로노이  (편출)</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-1829256000</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>0.43%→0.00%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>11→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>886485600</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>2.66%→2.88%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>149→160</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>에이치브이엠</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-409344000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.22%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>34→24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>353748000</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>2.90%→2.70%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>166→171</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-371509200</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>0.60%→0.43%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>56→47</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B21" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C21" s="11" t="n">
         <v>480585600</v>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>1.23%→1.39%</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>1.25%→1.39%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>36→39</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>에이치브이엠</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>-409344000</v>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>0.34%→0.22%</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>34→24</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>보로노이  (편출)</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>-1471867200</v>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>0.31%→0.00%</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>9→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I20" s="15" t="n">
+      <c r="I21" s="15" t="n">
         <v>-969141600</v>
       </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>0.44%→0.31%</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.41%→0.31%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>17→10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>코오롱생명과학</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>-190404000</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>0.39%→0.28%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>45→39</t>
         </is>
       </c>
     </row>
@@ -1319,1163 +1372,1477 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
+          <t>코오롱생명과학</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-190404000</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.28%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>45→39</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
           <t>올릭스</t>
         </is>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H23" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I22" s="15" t="n">
+      <c r="I23" s="15" t="n">
         <v>-403243200</v>
       </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>1.74%→1.95%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>1.90%→1.95%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>68→65</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 22억(0.5%)      오늘 2026-07-20  vs  5일전 2026-07-13      매수 3종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 22억(0.5%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>HLB이노베이션</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>507329200</v>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>1.15%→1.58%</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>983→1,066</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>오스코텍</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>-49</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>-871636500</v>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>2.96%→2.81%</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>701→652</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1204308000</v>
+        <v>507329200</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>7.59%→7.66%</t>
+          <t>1.67%→1.58%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>682→709</t>
+          <t>983→1,066</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-21</v>
+        <v>-49</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-372319500</v>
+        <v>-871636500</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>1.79%→1.48%</t>
+          <t>3.03%→2.81%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>366→345</t>
+          <t>701→652</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>1204308000</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>7.60%→7.66%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>682→709</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-372319500</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>1.65%→1.48%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>366→345</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B30" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C30" s="11" t="n">
         <v>978810000</v>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>8.20%→7.58%</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>7.72%→7.58%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>186→192</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>녹십자</t>
         </is>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H30" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I29" s="15" t="n">
+      <c r="I30" s="15" t="n">
         <v>-869424000</v>
       </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>3.27%→3.21%</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>3.26%→3.21%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>195→183</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="19" t="n"/>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 4억(100.0%)      오늘 2026-07-20  vs  5일전 2026-07-13      매수 9종목  /  매도 14종목</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 51억(1.9%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>3186713200</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>2.23%→2.42%</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>120→242</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-451</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-11964939800</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>7.82%→3.03%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>750→299</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>6573593400</v>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>1.43%→4.23%</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>61→150</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>-3582887000</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>3.97%→2.16%</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>49→30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>6151094400</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>4.92%→7.35%</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>102→150</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>78633500</v>
+        <v>2650252000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>6.47%→6.69%</t>
+          <t>6.66%→9.62%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>3,229→3,339</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-174</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>-44000250</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>0.43%→0.30%</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>601→427</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>96</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>342312000</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>6.34%→7.29%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>634→730</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>금양그린파워</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-63525600</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>0.95%→0.77%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>574→466</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>175185000</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>2.51%→3.00%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>460→550</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-73</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-93075000</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>1.51%→1.25%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>422→349</t>
-        </is>
-      </c>
+          <t>170→190</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="n"/>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="17" t="n"/>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 50억(2.0%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>206231250</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>5.38%→5.95%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>697→772</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>액트로</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-29</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-20385550</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>0.36%→0.30%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>183→154</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>136467500</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>2.42%→2.80%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>240→278</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-56100000</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>0.60%→0.44%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>95→70</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>103581000</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>2.11%→2.40%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>131→149</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-37194300</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>0.40%→0.30%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>85→63</t>
-        </is>
-      </c>
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 4억(100.0%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 11종목  /  매도 15종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>40749000</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>1.05%→1.16%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>55→61</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-172601000</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>3.72%→3.24%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>100→87</t>
-        </is>
-      </c>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>심텍</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>62016000</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>2.12%→2.29%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>73→79</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-145554000</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>3.30%→2.89%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>97→85</t>
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>34892500</v>
+        <v>141540300</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.10%→0.20%</t>
+          <t>6.26%→6.69%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>5→10</t>
+          <t>3,141→3,339</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-174</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-44000250</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.30%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>601→427</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>99</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>192703500</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2.45%→3.00%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>451→550</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-63525600</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.94%→0.77%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>574→466</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>342312000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>6.30%→7.29%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>634→730</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-73</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-93075000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>1.50%→1.25%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>422→349</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>206231250</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>5.34%→5.95%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>697→772</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>액트로</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-20385550</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.30%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>183→154</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>136467500</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>2.40%→2.80%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>240→278</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-56100000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.59%→0.44%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>103581000</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2.10%→2.40%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>131→149</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-216733000</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>4.47%→3.89%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>163→141</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>36975000</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>0.57%→0.68%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>83→98</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-37194300</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.40%→0.30%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>85→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>81498000</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>0.93%→1.16%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>49→61</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H46" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-163710000</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>3.88%→3.41%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>76→67</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>-88663500</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>4.15%→3.89%</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>150→141</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>-94307500</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>1.81%→1.55%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>48→41</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-66912000</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>0.28%→0.09%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>9→3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>기가비스</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-71017500</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>1.43%→1.23%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>36→31</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="17" t="n"/>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-57885000</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>2.54%→2.38%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>47→44</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 9억(1.7%)      오늘 2026-07-20  vs  5일전 2026-07-13      매수 3종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
+      <c r="H53" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-381990000</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>4.46%→3.41%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>88→67</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
-      <c r="K54" s="8" t="n"/>
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>31025000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>0.60%→0.69%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>69→79</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-172601000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>3.70%→3.24%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>100→87</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>62016000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>2.10%→2.29%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>73→79</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-145554000</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>3.28%→2.89%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>97→85</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
+          <t>코스메카코리아</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>34892500</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>0.10%→0.20%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>5→10</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-94307500</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>1.80%→1.55%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>48→41</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="n"/>
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-66912000</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>0.28%→0.09%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>9→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="n"/>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-86912500</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>3.49%→3.26%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>72→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-71017500</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>1.42%→1.23%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>36→31</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-57885000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>2.53%→2.38%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>47→44</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 9억(1.7%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
           <t>큐리오시스</t>
         </is>
       </c>
-      <c r="B56" s="11" t="n">
+      <c r="B65" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C56" s="11" t="n">
+      <c r="C65" s="11" t="n">
         <v>480704000</v>
       </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>1.59%→1.84%</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>1.53%→1.84%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>297→593</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>코오롱티슈진</t>
         </is>
       </c>
-      <c r="H56" s="15" t="n">
+      <c r="H65" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I56" s="15" t="n">
+      <c r="I65" s="15" t="n">
         <v>-244922400</v>
       </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>3.70%→2.24%</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>3.66%→2.24%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
         <is>
           <t>197→163</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="B57" s="11" t="n">
+      <c r="B66" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="C57" s="11" t="n">
+      <c r="C66" s="11" t="n">
         <v>570998400</v>
       </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>6.84%→8.37%</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>6.89%→8.37%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>187→215</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="H57" s="15" t="n">
+      <c r="H66" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I57" s="15" t="n">
+      <c r="I66" s="15" t="n">
         <v>-280627200</v>
       </c>
-      <c r="J57" s="16" t="inlineStr">
-        <is>
-          <t>7.06%→6.38%</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>7.08%→6.38%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
         <is>
           <t>413→381</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n">
+      <c r="B67" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C58" s="11" t="n">
+      <c r="C67" s="11" t="n">
         <v>702612000</v>
       </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>3.07%→4.77%</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>3.03%→4.77%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>46→64</t>
         </is>
       </c>
-      <c r="G58" s="14" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="H58" s="15" t="n">
+      <c r="H67" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I58" s="15" t="n">
+      <c r="I67" s="15" t="n">
         <v>-264642400</v>
       </c>
-      <c r="J58" s="16" t="inlineStr">
-        <is>
-          <t>9.02%→7.74%</t>
-        </is>
-      </c>
-      <c r="K58" s="13" t="inlineStr">
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>9.03%→7.74%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>359→337</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B60" s="19" t="n"/>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-      <c r="G60" s="19" t="n"/>
-      <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
-      <c r="J60" s="19" t="n"/>
-      <c r="K60" s="19" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="n"/>
+      <c r="F69" s="20" t="n"/>
+      <c r="G69" s="20" t="n"/>
+      <c r="H69" s="20" t="n"/>
+      <c r="I69" s="20" t="n"/>
+      <c r="J69" s="20" t="n"/>
+      <c r="K69" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A53:K53"/>
+  <mergeCells count="20">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G26:K26"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="G54:K54"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="G63:K63"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260720.xlsx
+++ b/reports/pdf_rolling5_20260720.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 151억(3.3%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 16종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,592억   ·   현금 152억(3.3%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 16종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>263</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3770599440</v>
+        <v>3801254720</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-78</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3016353600</v>
+        <v>-3040876800</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>231</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8705743200</v>
+        <v>8776521600</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-69</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-914559120</v>
+        <v>-921994560</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>207</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1892261520</v>
+        <v>1907645760</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-61</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1839735600</v>
+        <v>-1854692800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>80</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>952512000</v>
+        <v>960256000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-54</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-794914560</v>
+        <v>-801377280</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>70</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>4849152000</v>
+        <v>4888576000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1680868800</v>
+        <v>-1694534400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>59</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>985790880</v>
+        <v>993805440</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-32</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-810816000</v>
+        <v>-817408000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1840080000</v>
+        <v>1855040000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-701100000</v>
+        <v>-706800000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>26</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>3668745600</v>
+        <v>3698572800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-28</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-5353353600</v>
+        <v>-5396876800</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>891504000</v>
+        <v>898752000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-22</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1651742400</v>
+        <v>-1665171200</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>718566000</v>
+        <v>724408000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-20</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1212288000</v>
+        <v>-1222144000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>21</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>407700720</v>
+        <v>411015360</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-15</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-426564000</v>
+        <v>-430032000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>881172000</v>
+        <v>888336000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-13</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-410623200</v>
+        <v>-413961600</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>435666000</v>
+        <v>893692800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.72%</t>
+          <t>2.66%→2.88%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1219,7 +1219,7 @@
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1829256000</v>
+        <v>-1844128000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>886485600</v>
+        <v>439208000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.88%</t>
+          <t>0.62%→0.72%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>70→81</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1263,7 +1263,7 @@
         <v>-10</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-409344000</v>
+        <v>-412672000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>353748000</v>
+        <v>356624000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-371509200</v>
+        <v>-374529600</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>480585600</v>
+        <v>484492800</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-969141600</v>
+        <v>-977020800</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>-6</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-190404000</v>
+        <v>-191952000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>-3</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-403243200</v>
+        <v>-406521600</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 22억(0.5%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,085억   ·   현금 22억(0.5%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1519,7 +1519,7 @@
         <v>83</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>507329200</v>
+        <v>508189080</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>-49</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-871636500</v>
+        <v>-873113850</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1204308000</v>
+        <v>1206349200</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>-21</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-372319500</v>
+        <v>-372950550</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>978810000</v>
+        <v>980469000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>-12</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-869424000</v>
+        <v>-870897600</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 51억(1.9%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 52억(1.9%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1740,7 +1740,7 @@
         <v>122</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>3186713200</v>
+        <v>3233439200</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>-451</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-11964939800</v>
+        <v>-12140378800</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>89</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>6573593400</v>
+        <v>6669980400</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>-19</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-3582887000</v>
+        <v>-3635422000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>48</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>6151094400</v>
+        <v>6241286400</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2650252000</v>
+        <v>2689112000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 50억(2.0%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,453억   ·   현금 49억(2.0%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1901,7 +1901,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 4억(100.0%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 11종목  /  매도 15종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 4억(100.0%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 11종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1997,11 +1997,11 @@
         <v>198</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>141540300</v>
+        <v>136827900</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>6.26%→6.69%</t>
+          <t>6.44%→6.89%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2018,11 +2018,11 @@
         <v>-174</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-44000250</v>
+        <v>-42225450</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.30%</t>
+          <t>0.43%→0.31%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2041,11 +2041,11 @@
         <v>99</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>192703500</v>
+        <v>178398000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.45%→3.00%</t>
+          <t>2.41%→2.96%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2062,11 +2062,11 @@
         <v>-108</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-63525600</v>
+        <v>-61138800</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.77%</t>
+          <t>0.96%→0.79%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2085,11 +2085,11 @@
         <v>96</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>342312000</v>
+        <v>320688000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>6.30%→7.29%</t>
+          <t>6.29%→7.28%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2106,11 +2106,11 @@
         <v>-73</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-93075000</v>
+        <v>-91461700</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.50%→1.25%</t>
+          <t>1.57%→1.31%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2129,11 +2129,11 @@
         <v>75</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>206231250</v>
+        <v>191568750</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>5.34%→5.95%</t>
+          <t>5.29%→5.89%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2150,11 +2150,11 @@
         <v>-29</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-20385550</v>
+        <v>-19448850</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.30%</t>
+          <t>0.36%→0.31%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2173,11 +2173,11 @@
         <v>38</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>136467500</v>
+        <v>125647000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.40%→2.80%</t>
+          <t>2.36%→2.74%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2194,11 +2194,11 @@
         <v>-25</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-56100000</v>
+        <v>-50468750</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.44%</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2217,11 +2217,11 @@
         <v>18</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>103581000</v>
+        <v>94248000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.10%→2.40%</t>
+          <t>2.04%→2.33%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2231,23 +2231,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>오로스테크놀로지</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-216733000</v>
+        <v>-33753500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>4.47%→3.89%</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>163→141</t>
+          <t>85→63</t>
         </is>
       </c>
     </row>
@@ -2261,11 +2261,11 @@
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>36975000</v>
+        <v>36018750</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.68%</t>
+          <t>0.59%→0.70%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2275,23 +2275,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>오로스테크놀로지</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-37194300</v>
+        <v>-202521000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.30%</t>
+          <t>4.46%→3.88%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>85→63</t>
+          <t>163→141</t>
         </is>
       </c>
     </row>
@@ -2305,11 +2305,11 @@
         <v>12</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>81498000</v>
+        <v>71808000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.93%→1.16%</t>
+          <t>0.87%→1.09%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2326,11 +2326,11 @@
         <v>-21</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-381990000</v>
+        <v>-346825500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.41%</t>
+          <t>4.32%→3.30%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2349,11 +2349,11 @@
         <v>10</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>31025000</v>
+        <v>30642500</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.60%→0.69%</t>
+          <t>0.63%→0.72%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2370,11 +2370,11 @@
         <v>-13</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-172601000</v>
+        <v>-158457000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.70%→3.24%</t>
+          <t>3.62%→3.17%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2393,11 +2393,11 @@
         <v>6</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>62016000</v>
+        <v>54774000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.10%→2.29%</t>
+          <t>1.98%→2.15%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2414,11 +2414,11 @@
         <v>-12</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-145554000</v>
+        <v>-143514000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>3.28%→2.89%</t>
+          <t>3.44%→3.04%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2437,11 +2437,11 @@
         <v>5</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>34892500</v>
+        <v>36040000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.10%→0.20%</t>
+          <t>0.11%→0.22%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2458,11 +2458,11 @@
         <v>-7</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-94307500</v>
+        <v>-86275000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.80%→1.55%</t>
+          <t>1.76%→1.51%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2486,11 +2486,11 @@
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-66912000</v>
+        <v>-69666000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.09%</t>
+          <t>0.31%→0.10%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2507,23 +2507,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-86912500</v>
+        <v>-69190000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>3.49%→3.26%</t>
+          <t>1.48%→1.28%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>72→67</t>
+          <t>36→31</t>
         </is>
       </c>
     </row>
@@ -2535,23 +2535,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-71017500</v>
+        <v>-83045000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.23%</t>
+          <t>3.55%→3.32%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>36→31</t>
+          <t>72→67</t>
         </is>
       </c>
     </row>
@@ -2570,11 +2570,11 @@
         <v>-3</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-57885000</v>
+        <v>-54825000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.53%→2.38%</t>
+          <t>2.55%→2.40%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 9억(1.7%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 528억   ·   현금 9억(1.7%)      오늘 2026-07-20  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B62" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260720.xlsx
+++ b/reports/pdf_rolling5_20260720.xlsx
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>893692800</v>
+        <v>439208000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.88%</t>
+          <t>0.62%→0.72%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>70→81</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>439208000</v>
+        <v>893692800</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.72%</t>
+          <t>2.66%→2.88%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -2507,23 +2507,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-69190000</v>
+        <v>-83045000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.28%</t>
+          <t>3.55%→3.32%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>36→31</t>
+          <t>72→67</t>
         </is>
       </c>
     </row>
@@ -2535,23 +2535,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-83045000</v>
+        <v>-69190000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.32%</t>
+          <t>1.48%→1.28%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>72→67</t>
+          <t>36→31</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260720.xlsx
+++ b/reports/pdf_rolling5_20260720.xlsx
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>439208000</v>
+        <v>893692800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.72%</t>
+          <t>2.66%→2.88%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>893692800</v>
+        <v>439208000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.88%</t>
+          <t>0.62%→0.72%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>70→81</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260720.xlsx
+++ b/reports/pdf_rolling5_20260720.xlsx
@@ -2231,23 +2231,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>오로스테크놀로지</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-33753500</v>
+        <v>-202521000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.29%</t>
+          <t>4.46%→3.88%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>85→63</t>
+          <t>163→141</t>
         </is>
       </c>
     </row>
@@ -2275,23 +2275,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>오로스테크놀로지</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-202521000</v>
+        <v>-33753500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.88%</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>163→141</t>
+          <t>85→63</t>
         </is>
       </c>
     </row>
@@ -2507,23 +2507,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-83045000</v>
+        <v>-69190000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.32%</t>
+          <t>1.48%→1.28%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>72→67</t>
+          <t>36→31</t>
         </is>
       </c>
     </row>
@@ -2535,23 +2535,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-69190000</v>
+        <v>-83045000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.28%</t>
+          <t>3.55%→3.32%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>36→31</t>
+          <t>72→67</t>
         </is>
       </c>
     </row>
